--- a/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84CE10EC-E3D7-0044-B2EF-0BCA384048C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C389C9E-8A7B-6E47-9702-230BCB5BA647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="0" yWindow="4100" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="44">
   <si>
     <t>Coef Friction</t>
   </si>
@@ -3193,7 +3193,9 @@
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <v>0.85199999999999998</v>
+      </c>
       <c r="D5" s="3">
         <v>15000</v>
       </c>
@@ -3255,14 +3257,30 @@
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="34"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
+      <c r="C7" s="36">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D7" s="36">
+        <v>8000</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="39">
+        <v>1.5</v>
+      </c>
+      <c r="G7" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="36">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="36">
+        <v>400</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>12</v>
+      </c>
       <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">

--- a/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C389C9E-8A7B-6E47-9702-230BCB5BA647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA44793-7EEF-9D45-B00F-9F6F90108B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="4100" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
-    <sheet name="JB.V1" sheetId="10" r:id="rId2"/>
+    <sheet name="JB_V1" sheetId="10" r:id="rId2"/>
     <sheet name="C172" sheetId="3" r:id="rId3"/>
     <sheet name="B747" sheetId="6" r:id="rId4"/>
     <sheet name="TurboTilt" sheetId="8" r:id="rId5"/>

--- a/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA44793-7EEF-9D45-B00F-9F6F90108B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29ABB0F-EEF6-2847-8507-327EA944A1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4100" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="45">
   <si>
     <t>Coef Friction</t>
   </si>
@@ -173,6 +173,9 @@
   <si>
     <t>Max Mach (Max Speed)</t>
   </si>
+  <si>
+    <t>Max Sustained Turn</t>
+  </si>
 </sst>
 </file>
 
@@ -234,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -470,24 +473,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -497,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -529,20 +521,28 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="72">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2315,80 +2315,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EA520BC-547E-FB42-9345-C10BE812E714}" name="Table326" displayName="Table326" ref="A1:K187" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EA520BC-547E-FB42-9345-C10BE812E714}" name="Table326" displayName="Table326" ref="A1:K187" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A1:K187" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E873125-B430-DF47-97E8-8718CA85A22C}" name="Requirement #" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{F52F1F07-B543-0B47-8053-E34E2BA8895A}" name="Requirement Type" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{FE328122-9A74-7A4B-B57D-BF029EDE1844}" name="Input 1" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{418B51CA-8898-B442-BEE4-8304BF1CD6C0}" name="Input 2" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{A456BF20-760C-3A48-A400-7558B03C7A73}" name="Input 3" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{C9B3AF7B-40A5-7A4B-954F-08C72C3E8D95}" name="Input 4" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{A6995574-966C-AA49-8F26-8C85A4851905}" name="Input 5" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{976E4B5C-CC56-E948-9B3D-4F36230C9950}" name="Input 6" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{D10F34FA-7944-934F-B09F-BFE9ED3EFBC2}" name="Input 7" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{C3452EA2-25EF-274F-BAF6-358D378B7C56}" name="Input 8" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{95D5D1CA-CE7A-B245-9964-B82D986B951F}" name="Input 9" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{4E873125-B430-DF47-97E8-8718CA85A22C}" name="Requirement #" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{F52F1F07-B543-0B47-8053-E34E2BA8895A}" name="Requirement Type" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{FE328122-9A74-7A4B-B57D-BF029EDE1844}" name="Input 1" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{418B51CA-8898-B442-BEE4-8304BF1CD6C0}" name="Input 2" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{A456BF20-760C-3A48-A400-7558B03C7A73}" name="Input 3" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{C9B3AF7B-40A5-7A4B-954F-08C72C3E8D95}" name="Input 4" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{A6995574-966C-AA49-8F26-8C85A4851905}" name="Input 5" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{976E4B5C-CC56-E948-9B3D-4F36230C9950}" name="Input 6" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{D10F34FA-7944-934F-B09F-BFE9ED3EFBC2}" name="Input 7" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{C3452EA2-25EF-274F-BAF6-358D378B7C56}" name="Input 8" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{95D5D1CA-CE7A-B245-9964-B82D986B951F}" name="Input 9" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16D9459C-59A6-BF4A-A7B6-FBED165ADCA1}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55" tableBorderDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16D9459C-59A6-BF4A-A7B6-FBED165ADCA1}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56" tableBorderDxfId="55">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{05E785CD-BA1A-0741-A8C1-F103F004A333}" name="Requirement #" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{65ED0781-559E-BB4A-95BC-C03BEB6F0FD3}" name="Requirement Type" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{A5BC6781-8D14-CA4A-8CC8-894BC40040CF}" name="Input 1" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{426A3784-CB12-634C-B28C-1912BBEDA639}" name="Input 2" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{6CB1F183-1B01-524E-A8C5-EFDF25C9EC6E}" name="Input 3" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{018A88FF-960F-EE4D-AA98-1781DA96E06D}" name="Input 4" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{DA0F16CA-219B-2C46-8309-C7D52FE83C6B}" name="Input 5" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{9E89BB34-08B2-3641-902A-0475DC098911}" name="Input 6" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{BC7719A6-3F10-F04A-ADE2-39707C03237F}" name="Input 7" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{B83931B8-07AE-B044-9121-BD48FE4CFC72}" name="Input 8" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{A1FD63F7-D5E1-E742-9C9A-DB3936B5DD1F}" name="Input 9" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{05E785CD-BA1A-0741-A8C1-F103F004A333}" name="Requirement #" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{65ED0781-559E-BB4A-95BC-C03BEB6F0FD3}" name="Requirement Type" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{A5BC6781-8D14-CA4A-8CC8-894BC40040CF}" name="Input 1" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{426A3784-CB12-634C-B28C-1912BBEDA639}" name="Input 2" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{6CB1F183-1B01-524E-A8C5-EFDF25C9EC6E}" name="Input 3" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{018A88FF-960F-EE4D-AA98-1781DA96E06D}" name="Input 4" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{DA0F16CA-219B-2C46-8309-C7D52FE83C6B}" name="Input 5" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{9E89BB34-08B2-3641-902A-0475DC098911}" name="Input 6" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{BC7719A6-3F10-F04A-ADE2-39707C03237F}" name="Input 7" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{B83931B8-07AE-B044-9121-BD48FE4CFC72}" name="Input 8" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{A1FD63F7-D5E1-E742-9C9A-DB3936B5DD1F}" name="Input 9" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9925791-6FE9-D24F-854A-AA3A87983F7A}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41" tableBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9925791-6FE9-D24F-854A-AA3A87983F7A}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42" tableBorderDxfId="41">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{79B11DD2-72B5-A244-9BA2-010F65DA0C71}" name="Requirement #" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{A92F991A-F478-DF49-9573-45217E106A85}" name="Requirement Type" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{426F7ACD-E846-6B45-8580-16C9BC5B34B5}" name="Input 1" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{D8AF62F2-8523-1145-A81E-A1364337806B}" name="Input 2" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{84BDE2D1-2330-CF41-AEE0-9F5842569747}" name="Input 3" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{FE5DDCDE-FABD-E946-863B-C6BB28097755}" name="Input 4" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{18A756AC-E9D0-6E49-A4DE-24B7F35F91C5}" name="Input 5" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{21B200F8-22B2-0648-80FC-4820DECF0D5B}" name="Input 6" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{CB23FB5A-7884-AD4D-B71C-6E6EDDBF2886}" name="Input 7" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{40228DA8-61D6-1647-A4A3-EDA3C2FFFECB}" name="Input 8" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{F6825A5F-3D00-6E44-B99F-13492A664278}" name="Input 9" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{79B11DD2-72B5-A244-9BA2-010F65DA0C71}" name="Requirement #" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{A92F991A-F478-DF49-9573-45217E106A85}" name="Requirement Type" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{426F7ACD-E846-6B45-8580-16C9BC5B34B5}" name="Input 1" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{D8AF62F2-8523-1145-A81E-A1364337806B}" name="Input 2" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{84BDE2D1-2330-CF41-AEE0-9F5842569747}" name="Input 3" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{FE5DDCDE-FABD-E946-863B-C6BB28097755}" name="Input 4" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{18A756AC-E9D0-6E49-A4DE-24B7F35F91C5}" name="Input 5" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{21B200F8-22B2-0648-80FC-4820DECF0D5B}" name="Input 6" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{CB23FB5A-7884-AD4D-B71C-6E6EDDBF2886}" name="Input 7" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{40228DA8-61D6-1647-A4A3-EDA3C2FFFECB}" name="Input 8" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{F6825A5F-3D00-6E44-B99F-13492A664278}" name="Input 9" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70" tableBorderDxfId="69">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3042,12 +3042,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:I6">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J4 B7:J14">
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3110,49 +3110,49 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="34">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
       <c r="K2" s="17"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37">
+      <c r="A3" s="35"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38">
         <v>8000</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="38">
         <v>1.5</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="38">
         <v>30.414200000000001</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
       <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -3222,92 +3222,126 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
+      <c r="A6" s="35">
         <v>3</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="H6" s="38" t="s">
+      <c r="H6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="39" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="36">
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="37">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="37">
         <v>8000</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="40">
         <v>1.5</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="37">
         <v>0.2</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="37">
         <v>0.1</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="37">
         <v>400</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="37" t="s">
         <v>12</v>
       </c>
       <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="31"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="17"/>
+      <c r="A8" s="34">
+        <v>4</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="41" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="17"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D9" s="33">
+        <v>8000</v>
+      </c>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33">
+        <v>1</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -5624,18 +5658,18 @@
       <c r="K187" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:XFD1 B8:K8 L2:XFD1048576 A9:K1048576 K6:K7 G2:K3">
-    <cfRule type="expression" dxfId="12" priority="5">
+  <conditionalFormatting sqref="A1:B1 D1:XFD1 L2:XFD1048576 A10:K1048576 K6:K7 G2:K3 A9">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:J7">
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:K5">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8537,17 +8571,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD3 J4:XFD4 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11449,17 +11483,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD4 C5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14313,22 +14347,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 F2:XFD2 B3:XFD3 J4:XFD4 B4:K11 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29ABB0F-EEF6-2847-8507-327EA944A1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404CA4F6-FE07-7546-966A-CD486F87C1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
@@ -181,7 +181,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -213,6 +213,12 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
@@ -523,7 +529,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -532,6 +537,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3110,49 +3116,49 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="35">
+      <c r="A2" s="34">
         <v>1</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
       <c r="K2" s="17"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="35"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38">
+      <c r="A3" s="34"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37">
         <v>8000</v>
       </c>
-      <c r="D3" s="38">
+      <c r="D3" s="37">
         <v>1.5</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="37">
         <v>30.414200000000001</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
       <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -3222,124 +3228,124 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="35">
+      <c r="A6" s="34">
         <v>3</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="39" t="s">
+      <c r="G6" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="H6" s="39" t="s">
+      <c r="H6" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="38" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="37">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="36">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="36">
         <v>8000</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="39">
         <v>1.5</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="36">
         <v>0.2</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="36">
         <v>0.1</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="36">
         <v>400</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="36" t="s">
         <v>12</v>
       </c>
       <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
+      <c r="A8" s="33">
         <v>4</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="41" t="s">
+      <c r="K8" s="40" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="32"/>
-      <c r="C9" s="33">
+      <c r="C9" s="41">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="41">
         <v>8000</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33">
+      <c r="E9" s="41"/>
+      <c r="F9" s="41">
         <v>1</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33">
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41">
         <v>0.1</v>
       </c>
-      <c r="K9" s="33" t="s">
+      <c r="K9" s="41" t="s">
         <v>44</v>
       </c>
     </row>
